--- a/faculty.xlsx
+++ b/faculty.xlsx
@@ -5838,8 +5838,7 @@
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>生物物理 / 統計物理 / 場論  &lt;br&gt;
-&lt;a href="http://sansan.phy.ncu.edu.tw/~hclee/index.html" rel="noopener" target="_blank"&gt;個人學術網頁&lt;/a&gt;</t>
+          <t>生物物理、統計物理、場論</t>
         </is>
       </c>
       <c r="O53" t="inlineStr">
@@ -5968,6 +5967,11 @@
       <c r="N57" t="inlineStr">
         <is>
           <t>原子分子物理 / 表面物理</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>files/faculty/專任及退休師資照片/李敬萱.webp</t>
         </is>
       </c>
     </row>

--- a/faculty.xlsx
+++ b/faculty.xlsx
@@ -1150,7 +1150,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I13"/>
+  <dimension ref="A1:I14"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="4"/>
@@ -1308,7 +1308,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -1663,6 +1663,31 @@
       <c r="I13" t="inlineStr">
         <is>
           <t>理論量子光學研究室</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>1</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>施凱文</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>專任助理</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>S4-715</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>kevincatstudy09072@gmail.com</t>
         </is>
       </c>
     </row>
@@ -2926,7 +2951,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S63"/>
+  <dimension ref="A1:S64"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="2"/>
@@ -7650,6 +7675,41 @@
       <c r="S63" s="3" t="inlineStr">
         <is>
           <t>Photoelectronic Materials / Semiconductor Physics</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>1</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>在職</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>胡皓為</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>助理教授</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>haoweihu0311@gmail.com</t>
+        </is>
+      </c>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t>Hao-Wei Hu</t>
+        </is>
+      </c>
+      <c r="R64" t="inlineStr">
+        <is>
+          <t>Assistant Professor</t>
         </is>
       </c>
     </row>
@@ -9157,7 +9217,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -9222,7 +9282,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
